--- a/data/reports/PHASE_10_EVENING_MODEL.xlsx
+++ b/data/reports/PHASE_10_EVENING_MODEL.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -660,17 +660,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -680,7 +680,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -720,7 +720,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -730,27 +730,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -760,7 +760,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>05</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -770,7 +770,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1138,7 +1138,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -1418,7 +1418,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>038</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1448,17 +1448,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>038</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>056</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1488,7 +1488,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>269</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1498,7 +1498,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B14" t="n">
